--- a/MSME/BRD - Test Doc/MSME_CG_Final_2Decimal.xlsx
+++ b/MSME/BRD - Test Doc/MSME_CG_Final_2Decimal.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" activeTab="2"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="New_CG" sheetId="1" r:id="rId1"/>
@@ -390,7 +390,7 @@
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,13 +422,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -940,137 +933,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
@@ -1089,12 +1082,11 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1599,10 +1591,10 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="18">
+      <c r="A2" s="17">
         <v>46199</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="17">
         <v>46296</v>
       </c>
       <c r="C2">
@@ -1644,10 +1636,10 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="18">
+      <c r="A3" s="17">
         <v>46199</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>47027</v>
       </c>
       <c r="C3">
@@ -1689,10 +1681,10 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="18">
+      <c r="A4" s="17">
         <v>46054</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>46209</v>
       </c>
       <c r="C4">
@@ -2564,169 +2556,169 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="7">
         <v>2</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>180000000</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="12">
         <v>180000000</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>50000000</v>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="14">
         <f>MAX(0,G2+H2-I2)</f>
         <v>310000000</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="7">
         <f>YEAR(D2)-IF(MONTH(D2)&lt;4,1,0)-YEAR(C2)+IF(MONTH(C2)&lt;4,1,0)+1</f>
         <v>4</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="7">
         <v>2</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="15">
         <f>IF(E2=2,0.005,IF(K2&lt;=4,0.015,0.01))</f>
         <v>0.005</v>
       </c>
-      <c r="N2" s="17">
+      <c r="N2" s="16">
         <f>IF(OR(F2="NPA",F2="CLOSE"),0,J2*M2)</f>
         <v>1550000</v>
       </c>
-      <c r="O2" s="17">
+      <c r="O2" s="16">
         <f>IF(OR(F2="NPA",F2="CLOSE"),0,N2*L2)</f>
         <v>3100000</v>
       </c>
-      <c r="P2" s="17">
+      <c r="P2" s="16">
         <f>N2+O2</f>
         <v>4650000</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="7">
         <v>1</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>1000000000</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <v>1000000000</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>50000000</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="14">
         <f>MAX(0,G3+H3-I3)</f>
         <v>1950000000</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="7">
         <f>YEAR(D3)-IF(MONTH(D3)&lt;4,1,0)-YEAR(C3)+IF(MONTH(C3)&lt;4,1,0)+1</f>
         <v>4</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="7">
         <v>2</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="15">
         <f>IF(E3=2,0.005,IF(K3&lt;=4,0.015,0.01))</f>
         <v>0.015</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="16">
         <f>IF(OR(F3="NPA",F3="CLOSE"),0,J3*M3)</f>
         <v>29250000</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="16">
         <f>IF(OR(F3="NPA",F3="CLOSE"),0,N3*L3)</f>
         <v>58500000</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="16">
         <f>N3+O3</f>
         <v>87750000</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="7">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>1000000000</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>1000000000</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>50000000</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="14">
         <f>MAX(0,G4+H4-I4)</f>
         <v>1950000000</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="7">
         <f>YEAR(D4)-IF(MONTH(D4)&lt;4,1,0)-YEAR(C4)+IF(MONTH(C4)&lt;4,1,0)+1</f>
         <v>4</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="7">
         <v>2</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="15">
         <f>IF(E4=2,0.005,IF(K4&lt;=4,0.015,0.01))</f>
         <v>0.015</v>
       </c>
-      <c r="N4" s="17">
+      <c r="N4" s="16">
         <f>IF(OR(F4="NPA",F4="CLOSE"),0,J4*M4)</f>
         <v>29250000</v>
       </c>
-      <c r="O4" s="17">
+      <c r="O4" s="16">
         <f>IF(OR(F4="NPA",F4="CLOSE"),0,N4*L4)</f>
         <v>58500000</v>
       </c>
-      <c r="P4" s="17">
+      <c r="P4" s="16">
         <f>N4+O4</f>
         <v>87750000</v>
       </c>
@@ -2794,38 +2786,38 @@
     </row>
     <row r="2" s="7" customFormat="1" spans="1:9">
       <c r="A2" s="9">
-        <v>47587</v>
+        <v>47345</v>
       </c>
       <c r="B2" s="9">
         <f>DATE(YEAR(A2)-(MONTH(A2)&lt;4),3,31)</f>
-        <v>47573</v>
+        <v>47208</v>
       </c>
       <c r="C2" s="9">
         <v>47452</v>
       </c>
       <c r="D2" s="9">
         <f>A2-180</f>
-        <v>47407</v>
+        <v>47165</v>
       </c>
       <c r="E2" s="9">
         <f>DATE(YEAR(A2)-1-(MONTH(A2)&lt;4),4,1)</f>
-        <v>47209</v>
+        <v>46844</v>
       </c>
       <c r="F2" s="9">
         <f>MAX(D2,E2)</f>
-        <v>47407</v>
+        <v>47165</v>
       </c>
       <c r="G2" s="9">
         <f>B2</f>
-        <v>47573</v>
+        <v>47208</v>
       </c>
       <c r="H2" s="8">
         <f>A2-C2</f>
-        <v>135</v>
+        <v>-107</v>
       </c>
       <c r="I2" s="8" t="str">
         <f>IF(AND(C2&gt;=F2,C2&lt;=G2),"Valid","Invalid")</f>
-        <v>Valid</v>
+        <v>Invalid</v>
       </c>
     </row>
   </sheetData>
